--- a/backend/data/templates/campus_data_template.xlsx
+++ b/backend/data/templates/campus_data_template.xlsx
@@ -3,13 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Buildings" sheetId="1" r:id="rId1"/>
-    <sheet name="Locations_and_Facilities" sheetId="2" r:id="rId2"/>
-    <sheet name="Faculty_Directory" sheetId="3" r:id="rId3"/>
-    <sheet name="Departments" sheetId="4" r:id="rId4"/>
-    <sheet name="Services_and_Timings" sheetId="5" r:id="rId5"/>
-    <sheet name="Bus_Schedules" sheetId="6" r:id="rId6"/>
-    <sheet name="Campus_Policies" sheetId="7" r:id="rId7"/>
+    <sheet name="README_Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Buildings" sheetId="2" r:id="rId2"/>
+    <sheet name="Locations_and_Facilities" sheetId="3" r:id="rId3"/>
+    <sheet name="Faculty_Directory" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="5" r:id="rId5"/>
+    <sheet name="Paths" sheetId="6" r:id="rId6"/>
+    <sheet name="Services" sheetId="7" r:id="rId7"/>
+    <sheet name="Bus_Routes" sheetId="8" r:id="rId8"/>
+    <sheet name="Office_Hours" sheetId="9" r:id="rId9"/>
+    <sheet name="Academic_Calendar" sheetId="10" r:id="rId10"/>
+    <sheet name="Important_Dates" sheetId="11" r:id="rId11"/>
+    <sheet name="Holidays" sheetId="12" r:id="rId12"/>
+    <sheet name="Campus_Policies" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -403,111 +409,702 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Step</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Guideline</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1. Choose Your Data Sheet</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Each tab in this workbook corresponds to a core campus AI knowledge layer (Buildings, Facilities, Faculty, Departments, Paths, Services, Schedules, Policies).</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2. Mandatory Fields (*)</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Columns marked with an asterisk (*) are required for proper indexing into Kryvix's knowledge base and vector memory.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3. Comma-Separated Values</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fields like Aliases, Tags, Programs, and Nearby Buildings accept comma-separated strings without quotes.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4. GPS Coordinates</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Latitude and Longitude should be decimal format (e.g. 22.288408, 73.363971). They enable interactive campus map routing.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5. Single-Sheet Uploads</v>
+      </c>
+      <c r="B6" t="str">
+        <v>You can upload this entire master workbook, or extract and upload individual sheets / CSVs. Kryvix automatically identifies the data type.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6. Instant Vector Embedding</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Upon upload in the Admin Documents Hub, all records are immediately vectorized into the AI memory without server restarts.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Academic Year*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Semester*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Semester Name*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>End Date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Exam Start</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Exam End</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Result Declaration</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B2" t="str">
+        <v>odd_sem_2026</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Odd Semester (Autumn 2026)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-12-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-12-24</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2027-01-20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B3" t="str">
+        <v>even_sem_2027</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Even Semester (Spring 2027)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2027-01-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2027-05-15</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2027-05-20</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2027-06-10</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2027-07-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Academic Year*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Event*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Date*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Commencement of Classes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="D2" t="str">
+        <v>First day of instruction for all undergraduate and postgraduate engineering semesters.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Last Date for Term Fee Payment</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Late fee applies after this deadline through the student portal.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Mid-Semester Internal Examinations</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Central internal evaluation exams across all affiliated colleges.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Academic Year*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Holiday Note</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Fixed National Holidays (one per row)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Classes and offices remain suspended on official holidays. Essential services remain operational.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Independence Day - 15 August 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Emergency health center and hostel mess remain open during vacation periods.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mahatma Gandhi Jayanti - 02 October 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>Diwali Vacation - 28 October to 04 November 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-2027</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>Republic Day - 26 January 2027</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Policy Title*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Category*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Tags (comma-separated)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Aliases (comma-separated)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Content*</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Attendance Policy</v>
+      </c>
+      <c r="B2" t="str">
+        <v>academic</v>
+      </c>
+      <c r="C2" t="str">
+        <v>attendance, 75 percent, rules, condonation, detained, eligibility</v>
+      </c>
+      <c r="D2" t="str">
+        <v>attendance rule, minimum attendance, attendance shortage</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Parul University mandates a minimum attendance of 75% in each enrolled subject to appear for end-semester examinations. Students with attendance between 65% and 74% may apply for condonation on valid medical grounds through their Department HOD with valid medical certificates within 7 days. Students with attendance below 65% are strictly detained and must repeat the course.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Anti-Ragging Zero Tolerance Policy</v>
+      </c>
+      <c r="B3" t="str">
+        <v>discipline</v>
+      </c>
+      <c r="C3" t="str">
+        <v>anti ragging, discipline, safety, helpline, ufc</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ragging rule, anti ragging cell, safety helpline</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Parul University enforces a strict Zero Tolerance Policy against any form of ragging or harassment on campus, in hostels, or on university transport. Any violation leads to immediate suspension, rustication, and police FIR registration under UGC regulations. The 24/7 Anti-Ragging Helpline is available to all students.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Building Code*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Building Name*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Short Name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Floors</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Zone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Latitude</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Longitude</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Aliases (comma-separated)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Institutes</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Nearby Buildings</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Parul Institute of Engineering &amp; Technology</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PIET</v>
+      </c>
+      <c r="D2" t="str">
+        <v>academic</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" t="str">
+        <v>central</v>
+      </c>
+      <c r="G2">
+        <v>22.288408</v>
+      </c>
+      <c r="H2">
+        <v>73.363971</v>
+      </c>
+      <c r="I2" t="str">
+        <v>PIET, A1, engineering block, A block</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Main engineering and technology block of Parul University.</v>
+      </c>
+      <c r="K2" t="str">
+        <v>PIET, Faculty of Engineering</v>
+      </c>
+      <c r="L2" t="str">
+        <v>A2, A3, C1, C2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>C1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Administrative Block C1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Admin C1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="str">
+        <v>central</v>
+      </c>
+      <c r="G3">
+        <v>22.2891</v>
+      </c>
+      <c r="H3">
+        <v>73.3645</v>
+      </c>
+      <c r="I3" t="str">
+        <v>admin block, main office, exam section</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Houses university leadership, registrar, exam section, and accounts.</v>
+      </c>
+      <c r="K3" t="str">
+        <v>University Administration</v>
+      </c>
+      <c r="L3" t="str">
+        <v>C2, PU Circle</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Location / Facility Name*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Type*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Building Code*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Floor*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Room / Landmark</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Gender (for washrooms)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Aliases (comma-separated)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes / Details</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Placement Cell</v>
+      </c>
+      <c r="B2" t="str">
+        <v>office</v>
+      </c>
+      <c r="C2" t="str">
+        <v>C1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Room 202, near central stairs</v>
+      </c>
+      <c r="F2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="G2" t="str">
+        <v>placement office, tpo, career cell</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Coordinates campus placements and corporate drives.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Central Washroom</v>
+      </c>
+      <c r="B3" t="str">
+        <v>washroom</v>
+      </c>
+      <c r="C3" t="str">
+        <v>A1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Ground floor near north entrance</v>
+      </c>
+      <c r="F3" t="str">
+        <v>both</v>
+      </c>
+      <c r="G3" t="str">
+        <v>restroom, washroom, toilet</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Separate accessible facilities for students and staff.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>HDFC &amp; SBI ATM</v>
+      </c>
+      <c r="B4" t="str">
+        <v>atm</v>
+      </c>
+      <c r="C4" t="str">
+        <v>C1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Ground floor exterior portico</v>
+      </c>
+      <c r="F4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="G4" t="str">
+        <v>atm, cash machine, bank atm</v>
+      </c>
+      <c r="H4" t="str">
+        <v>24/7 cash withdrawal and passbook printing.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Name*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Role / Designation*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Department*</v>
+      </c>
+      <c r="D1" t="str">
         <v>Building Code*</v>
       </c>
-      <c r="B1" t="str">
-        <v>Full Building Name*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Short Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Category</v>
-      </c>
       <c r="E1" t="str">
-        <v>Floors</v>
+        <v>Floor</v>
       </c>
       <c r="F1" t="str">
-        <v>Zone</v>
+        <v>Cabin/Room</v>
       </c>
       <c r="G1" t="str">
-        <v>Latitude</v>
+        <v>Email</v>
       </c>
       <c r="H1" t="str">
-        <v>Longitude</v>
+        <v>Phone</v>
       </c>
       <c r="I1" t="str">
+        <v>Subjects Taught</v>
+      </c>
+      <c r="J1" t="str">
         <v>Aliases (comma-separated)</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Description</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Nearby Buildings</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A1</v>
+        <v>Dr. Alpesh Desai</v>
       </c>
       <c r="B2" t="str">
-        <v>Parul Institute of Engineering &amp; Technology</v>
+        <v>Registrar</v>
       </c>
       <c r="C2" t="str">
-        <v>PIET</v>
+        <v>University Administration</v>
       </c>
       <c r="D2" t="str">
-        <v>academic</v>
+        <v>C1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>central</v>
-      </c>
-      <c r="G2">
-        <v>22.288408</v>
-      </c>
-      <c r="H2">
-        <v>73.363971</v>
+        <v>101</v>
+      </c>
+      <c r="G2" t="str">
+        <v>registrar@paruluniversity.ac.in</v>
+      </c>
+      <c r="H2" t="str">
+        <v>02668-260301</v>
       </c>
       <c r="I2" t="str">
-        <v>PIET, A1, engineering block, A block</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>Main engineering and technology block of Parul University.</v>
+        <v>registrar, registrar office, dr alpesh</v>
       </c>
       <c r="K2" t="str">
-        <v>A2, A3, C1, C2</v>
+        <v>Manages university records, statutory compliance, and correspondence.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C1</v>
+        <v>Prof. Rahul Sharma</v>
       </c>
       <c r="B3" t="str">
-        <v>Administrative Block C1</v>
+        <v>Assistant Professor</v>
       </c>
       <c r="C3" t="str">
-        <v>Admin C1</v>
+        <v>Computer Science &amp; Engineering</v>
       </c>
       <c r="D3" t="str">
-        <v>admin</v>
+        <v>A25</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>central</v>
-      </c>
-      <c r="G3">
-        <v>22.2891</v>
-      </c>
-      <c r="H3">
-        <v>73.3645</v>
+        <v>Cabin 312</v>
+      </c>
+      <c r="G3" t="str">
+        <v>rahul.sharma@paruluniversity.ac.in</v>
+      </c>
+      <c r="H3" t="str">
+        <v>02668-260450</v>
       </c>
       <c r="I3" t="str">
-        <v>admin block, main office, exam section</v>
+        <v>Data Structures, Algorithms</v>
       </c>
       <c r="J3" t="str">
-        <v>Houses university leadership, registrar, exam section, and accounts.</v>
+        <v>rahul sir, dsa faculty</v>
       </c>
       <c r="K3" t="str">
-        <v>C2, PU Circle</v>
+        <v>Faculty for BTech CSE students specializing in DSA and Competitive Coding.</v>
       </c>
     </row>
   </sheetData>
@@ -517,86 +1114,173 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Department Name*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Building Code*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Floor*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>HOD Name</v>
+      </c>
+      <c r="F1" t="str">
+        <v>HOD Email</v>
+      </c>
+      <c r="G1" t="str">
+        <v>HOD Room</v>
+      </c>
+      <c r="H1" t="str">
+        <v>HOD Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Programs Offered (comma-separated)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Aliases (comma-separated)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Subjects (comma-separated)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Computer Science &amp; Engineering</v>
+      </c>
+      <c r="B2" t="str">
+        <v>CSE</v>
+      </c>
+      <c r="C2" t="str">
+        <v>A25</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Dr. TBD</v>
+      </c>
+      <c r="F2" t="str">
+        <v>hod.cse@paruluniversity.ac.in</v>
+      </c>
+      <c r="G2" t="str">
+        <v>301</v>
+      </c>
+      <c r="H2" t="str">
+        <v>02668-260500</v>
+      </c>
+      <c r="I2" t="str">
+        <v>BTech CSE, BTech AI/ML, BTech Data Science, MTech CSE</v>
+      </c>
+      <c r="J2" t="str">
+        <v>CSE, computer science, cs department, btech cse</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Offers undergraduate and postgraduate programs with advanced coding labs.</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Programming, Operating Systems, Computer Networks, Machine Learning</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Location / Facility Name*</v>
+        <v>From Building Code*</v>
       </c>
       <c r="B1" t="str">
-        <v>Type*</v>
+        <v>From Building Name</v>
       </c>
       <c r="C1" t="str">
-        <v>Building Code*</v>
+        <v>To Building Code*</v>
       </c>
       <c r="D1" t="str">
-        <v>Floor*</v>
+        <v>To Building Name</v>
       </c>
       <c r="E1" t="str">
-        <v>Room / Landmark</v>
+        <v>Distance (m)*</v>
       </c>
       <c r="F1" t="str">
-        <v>Gender (for washrooms)</v>
+        <v>Walk Time (min)*</v>
       </c>
       <c r="G1" t="str">
-        <v>Aliases (comma-separated)</v>
+        <v>Route Description</v>
       </c>
       <c r="H1" t="str">
-        <v>Notes / Details</v>
+        <v>Landmarks (comma-separated)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Placement Cell</v>
+        <v>GATE_MAIN</v>
       </c>
       <c r="B2" t="str">
-        <v>office</v>
+        <v>Main Entry Gate</v>
       </c>
       <c r="C2" t="str">
-        <v>C1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Room 202, near central stairs</v>
-      </c>
-      <c r="F2" t="str">
-        <v>N/A</v>
+        <v>PU_CIRCLE</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Parul University Circle</v>
+      </c>
+      <c r="E2">
+        <v>80</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>placement office, tpo, career cell</v>
+        <v>Walk straight from the main security gate into campus. PU Circle is immediately ahead.</v>
       </c>
       <c r="H2" t="str">
-        <v>Coordinates campus placements and mock interviews.</v>
+        <v>Security Gate Post, PU Welcome Sign</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Central Washroom</v>
+        <v>PU_CIRCLE</v>
       </c>
       <c r="B3" t="str">
-        <v>washroom</v>
+        <v>Parul University Circle</v>
       </c>
       <c r="C3" t="str">
-        <v>A1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Ground floor near main entrance</v>
-      </c>
-      <c r="F3" t="str">
-        <v>both</v>
+        <v>C1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Administrative Block C1</v>
+      </c>
+      <c r="E3">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>restroom, washroom, toilet</v>
+        <v>From PU Circle, take the right fork towards admin zone. C1 is the large multi-story block on the right.</v>
       </c>
       <c r="H3" t="str">
-        <v>Separate facilities for male, female, and staff.</v>
+        <v>PU Circle, Visitor Parking P1</v>
       </c>
     </row>
   </sheetData>
@@ -606,394 +1290,250 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:M2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Faculty Name*</v>
+        <v>Service ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Role / Designation*</v>
+        <v>Service Name*</v>
       </c>
       <c r="C1" t="str">
-        <v>Department*</v>
+        <v>Type*</v>
       </c>
       <c r="D1" t="str">
         <v>Building Code*</v>
       </c>
       <c r="E1" t="str">
+        <v>Building Name</v>
+      </c>
+      <c r="F1" t="str">
         <v>Floor</v>
       </c>
-      <c r="F1" t="str">
-        <v>Room</v>
-      </c>
       <c r="G1" t="str">
-        <v>Email</v>
+        <v>Contact Email</v>
       </c>
       <c r="H1" t="str">
-        <v>Phone</v>
+        <v>Contact Phone</v>
       </c>
       <c r="I1" t="str">
-        <v>Subjects Taught</v>
+        <v>Aliases (comma-separated)</v>
       </c>
       <c r="J1" t="str">
-        <v>Aliases (comma-separated)</v>
+        <v>Timings (JSON)</v>
       </c>
       <c r="K1" t="str">
         <v>Description</v>
       </c>
+      <c r="L1" t="str">
+        <v>Facilities (comma-separated)</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Rules (comma-separated)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dr. Alpesh Desai</v>
+        <v>svc_001</v>
       </c>
       <c r="B2" t="str">
-        <v>Registrar</v>
+        <v>Central Library</v>
       </c>
       <c r="C2" t="str">
-        <v>University Administration</v>
+        <v>library</v>
       </c>
       <c r="D2" t="str">
         <v>C1</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="str">
+        <v>Administrative Block C1</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" t="str">
-        <v>101</v>
-      </c>
       <c r="G2" t="str">
-        <v>registrar@paruluniversity.ac.in</v>
+        <v>library@paruluniversity.ac.in</v>
       </c>
       <c r="H2" t="str">
-        <v>02668-260301</v>
+        <v>02668-260350</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>library, central library, reading room, book issue</v>
       </c>
       <c r="J2" t="str">
-        <v>registrar, registrar office, dr alpesh</v>
+        <v>{"monday_to_saturday": "07:00 AM - 08:00 PM", "sunday": "09:30 AM - 04:30 PM"}</v>
       </c>
       <c r="K2" t="str">
-        <v>Manages official university records, statutory compliance, and correspondence.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Prof. Rahul Sharma</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Assistant Professor</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Computer Science &amp; Engineering</v>
-      </c>
-      <c r="D3" t="str">
-        <v>A25</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Cabin 312</v>
-      </c>
-      <c r="G3" t="str">
-        <v>rahul.sharma@paruluniversity.ac.in</v>
-      </c>
-      <c r="H3" t="str">
-        <v>02668-260450</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Data Structures, Algorithms</v>
-      </c>
-      <c r="J3" t="str">
-        <v>rahul sir, dsa faculty</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Faculty for BTech CSE students specializing in DSA.</v>
+        <v>Central knowledge hub with over 100,000 volumes, IEEE access, and quiet study zones.</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Book issuing, Digital e-journals, Reading rooms, Photocopying</v>
+      </c>
+      <c r="M2" t="str">
+        <v>PU student ID card mandatory, Maintain silence, Bags not permitted inside</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Department Name*</v>
+        <v>Route ID*</v>
       </c>
       <c r="B1" t="str">
-        <v>Short Name</v>
+        <v>Route Name*</v>
       </c>
       <c r="C1" t="str">
-        <v>Building Code*</v>
+        <v>Route Number*</v>
       </c>
       <c r="D1" t="str">
-        <v>Floor*</v>
+        <v>Direction</v>
       </c>
       <c r="E1" t="str">
-        <v>HOD Name</v>
+        <v>Morning Departure</v>
       </c>
       <c r="F1" t="str">
-        <v>HOD Room</v>
+        <v>Stops (in order or JSON)</v>
       </c>
       <c r="G1" t="str">
-        <v>HOD Email</v>
+        <v>Return Schedule (JSON)</v>
       </c>
       <c r="H1" t="str">
-        <v>HOD Phone</v>
+        <v>Frequency</v>
       </c>
       <c r="I1" t="str">
-        <v>Programs (comma-separated)</v>
+        <v>Aliases (comma-separated)</v>
       </c>
       <c r="J1" t="str">
-        <v>Aliases (comma-separated)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Description</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Computer Science &amp; Engineering</v>
+        <v>PU-01</v>
       </c>
       <c r="B2" t="str">
-        <v>CSE</v>
+        <v>Vadodara Railway Station - Parul University</v>
       </c>
       <c r="C2" t="str">
-        <v>A25</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
+        <v>PU-01</v>
+      </c>
+      <c r="D2" t="str">
+        <v>both</v>
       </c>
       <c r="E2" t="str">
-        <v>Dr. TBD</v>
+        <v>07:00 AM</v>
       </c>
       <c r="F2" t="str">
-        <v>301</v>
+        <v>Vadodara Station -&gt; Fatehgunj -&gt; Amit Nagar -&gt; Waghodia Cross Road -&gt; PU Main Gate</v>
       </c>
       <c r="G2" t="str">
-        <v>hod.cse@paruluniversity.ac.in</v>
+        <v>["05:00 PM", "06:15 PM"]</v>
       </c>
       <c r="H2" t="str">
-        <v>02668-260500</v>
+        <v>Daily Monday to Saturday</v>
       </c>
       <c r="I2" t="str">
-        <v>BTech CSE, BTech AI/ML, BTech Data Science, MTech CSE</v>
+        <v>station bus, railway station bus, pu01</v>
       </c>
       <c r="J2" t="str">
-        <v>CSE, computer science, cs department, btech cse</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Offers undergraduate and postgraduate programs with advanced coding labs.</v>
+        <v>University bus pass must be displayed while boarding.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Service Name*</v>
+        <v>ID*</v>
       </c>
       <c r="B1" t="str">
-        <v>Type*</v>
+        <v>Name*</v>
       </c>
       <c r="C1" t="str">
-        <v>Building Code*</v>
+        <v>Days*</v>
       </c>
       <c r="D1" t="str">
-        <v>Floor</v>
+        <v>Timing*</v>
       </c>
       <c r="E1" t="str">
-        <v>Mon to Sat Timings</v>
+        <v>Lunch Break</v>
       </c>
       <c r="F1" t="str">
-        <v>Sunday Timings</v>
+        <v>Notes</v>
       </c>
       <c r="G1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="I1" t="str">
         <v>Aliases (comma-separated)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Facilities</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Rules</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Description</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Central Library</v>
+        <v>oh_001</v>
       </c>
       <c r="B2" t="str">
-        <v>library</v>
+        <v>Accounts &amp; Fee Counter</v>
       </c>
       <c r="C2" t="str">
-        <v>C1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>Monday to Saturday</v>
+      </c>
+      <c r="D2" t="str">
+        <v>09:00 AM - 04:30 PM</v>
       </c>
       <c r="E2" t="str">
-        <v>07:00 AM - 08:00 PM</v>
+        <v>01:00 PM - 01:45 PM</v>
       </c>
       <c r="F2" t="str">
-        <v>09:30 AM - 04:30 PM</v>
+        <v>Counter accepts fee challans, DDs, and online transaction verifications.</v>
       </c>
       <c r="G2" t="str">
-        <v>library@paruluniversity.ac.in</v>
-      </c>
-      <c r="H2" t="str">
-        <v>02668-260350</v>
-      </c>
-      <c r="I2" t="str">
-        <v>library, central library, reading room, book issue</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Book issuing, digital e-journals, reading rooms, NPTEL</v>
-      </c>
-      <c r="K2" t="str">
-        <v>ID card mandatory, silence, no food</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Network of over 10 subject-specific libraries linked to central system.</v>
+        <v>accounts office, fee counter, finance section</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>oh_002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Examination Section</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Monday to Friday</v>
+      </c>
+      <c r="D3" t="str">
+        <v>09:30 AM - 05:00 PM</v>
+      </c>
+      <c r="E3" t="str">
+        <v>01:15 PM - 02:00 PM</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Transcript requests, degree verification, and re-checking forms.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>exam office, grade card section, marksheet desk</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Route Number*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Route Name*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Morning Departure</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Stops (in order)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Return Schedule</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Frequency</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Aliases (comma-separated)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PU-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Vadodara Railway Station - Parul University</v>
-      </c>
-      <c r="C2" t="str">
-        <v>07:00 AM</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Station -&gt; Fatehgunj -&gt; Productivity Road -&gt; Waghodia -&gt; PU Main Gate</v>
-      </c>
-      <c r="E2" t="str">
-        <v>05:00 PM, 06:00 PM from Main Gate</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Once morning, twice evening</v>
-      </c>
-      <c r="G2" t="str">
-        <v>station bus, railway station bus, pu01</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Timings may vary during exams and holidays.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Policy Title*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Category*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tags (comma-separated)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Aliases (comma-separated)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Content*</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Attendance Policy</v>
-      </c>
-      <c r="B2" t="str">
-        <v>academic</v>
-      </c>
-      <c r="C2" t="str">
-        <v>attendance, 75 percent, rules, condonation, detained</v>
-      </c>
-      <c r="D2" t="str">
-        <v>attendance rule, minimum attendance, attendance shortage</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Parul University mandates a minimum attendance of 75% in each subject to appear for exams. Attendance is calculated subject-wise. Condonation for medical reasons (between 65% and 74%) may be requested through the HOD.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>